--- a/Accelerometer Parts List.xlsx
+++ b/Accelerometer Parts List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlguy\New Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF523F5C-990E-497D-BF81-F2E313DF2BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CC0599-26E1-45AE-BC05-07ACBE91EF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
   <si>
     <t>Part Description</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Size (in^2)</t>
   </si>
   <si>
-    <t>~5</t>
-  </si>
-  <si>
     <t>$5/in^2</t>
   </si>
   <si>
@@ -261,6 +258,12 @@
   </si>
   <si>
     <t>IZKE31-IIC-WH-3</t>
+  </si>
+  <si>
+    <t>Batteries - stack 2 3.6 V in series to get 7.2, it will get modulated to 5V by the Voltage Reg and then we can use it for the MicroSD</t>
+  </si>
+  <si>
+    <t>~3.07x2.4 = 7.4</t>
   </si>
 </sst>
 </file>
@@ -839,13 +842,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>12</v>
@@ -861,13 +864,13 @@
         <v>3.105</v>
       </c>
       <c r="H6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
         <v>60</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -1001,16 +1004,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1026,48 +1029,48 @@
         <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="E12" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="7">
         <v>0.1</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
         <v>72</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1083,10 +1086,15 @@
         <v>11.99</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1095,7 +1103,7 @@
       </c>
       <c r="G17" s="3">
         <f>SUM(G2:G13)</f>
-        <v>82.964999999999989</v>
+        <v>83.064999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1104,7 +1112,7 @@
       </c>
       <c r="G18" s="3">
         <f>SUM(G7:G13)</f>
-        <v>17.920000000000002</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -1121,25 +1129,26 @@
         <v>51</v>
       </c>
       <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
         <v>53</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" s="3">
+        <f>5*7.4</f>
+        <v>37</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G20" s="3">
-        <v>25</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="3">
         <f>G18+G20</f>
-        <v>42.92</v>
+        <v>55.019999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/Accelerometer Parts List.xlsx
+++ b/Accelerometer Parts List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlguy\New Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CC0599-26E1-45AE-BC05-07ACBE91EF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC813DD-81A4-4FDB-B984-6F36FB9C2E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="86">
   <si>
     <t>Part Description</t>
   </si>
@@ -236,21 +236,9 @@
     <t>Capacitor (Decoupling) MLCC 100nF 25V X7R</t>
   </si>
   <si>
-    <t>Capacitor (external input) 22uF 50V X7R</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/murata-electronics/KCM55QR71H226KH13K/16821350</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/gp/product/B076PDVFQD/</t>
   </si>
   <si>
-    <t>490-KCM55QR71H226KH13KCT-ND</t>
-  </si>
-  <si>
-    <t>KCM55QR71H226KH13K</t>
-  </si>
-  <si>
     <t>Diymall 0.96" Inch I2c IIC Serial 128x64 Oled LCD LED White Display Module (GND on Pin 1)</t>
   </si>
   <si>
@@ -264,6 +252,48 @@
   </si>
   <si>
     <t>~3.07x2.4 = 7.4</t>
+  </si>
+  <si>
+    <t>Capacitor (external input) 10uF 50V X5R</t>
+  </si>
+  <si>
+    <t>Walsin Technology Corporation</t>
+  </si>
+  <si>
+    <t>1206X106K500CT</t>
+  </si>
+  <si>
+    <t>1292-1206X106K500CT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/walsin-technology-corporation/1206X106K500CT/17808791</t>
+  </si>
+  <si>
+    <t>4 pin header for OLED screen</t>
+  </si>
+  <si>
+    <t>4 pin cable for OLED screen</t>
+  </si>
+  <si>
+    <t>1528-4936-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4936/14552171?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20232005509&amp;gbraid=0AAAAADrbLljFhl6uxaG6Vfs0W7q6jx3ii&amp;gclid=CjwKCAjwtvvPBhBuEiwAPMijr5ie0JUE-YVr1s3BIn2YI-rPrlRl3aUK7X-S9cMlmjBsBVxlI5H4CBoCar0QAvD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.adafruit.com/product/4936?srsltid=AfmBOoo60DuJxW7WVv9vNaFsUrHA5rsTkGxvHVOqGC14XekH9bkWL0r-</t>
+  </si>
+  <si>
+    <t>Harwin Inc.</t>
+  </si>
+  <si>
+    <t>M20-8770442</t>
+  </si>
+  <si>
+    <t>952-2353-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/harwin-inc/M20-8770442/3906342?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=17336967819&amp;gbraid=0AAAAADrbLljy55Q_fHYkiYfayGZku53Hu&amp;gclid=CjwKCAjwtvvPBhBuEiwAPMijrwmD32zTwh_m_WWuadgRad4clHmqjZAHfx3jsvLfpQkKoRUu3SWI_xoCH1IQAvD_BwE</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1019,7 @@
         <v>0.61</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G10:G15" si="1">E10*F10</f>
         <v>0.61</v>
       </c>
       <c r="H10" t="s">
@@ -1004,32 +1034,32 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" s="3">
-        <v>3.03</v>
+        <v>0.19</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="0"/>
-        <v>3.03</v>
+        <f t="shared" si="1"/>
+        <v>0.19</v>
       </c>
       <c r="H11" t="s">
         <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -1052,7 +1082,7 @@
         <v>0.1</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
       <c r="H12" s="6" t="s">
@@ -1064,13 +1094,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1082,19 +1112,76 @@
         <v>11.99</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.99</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="I14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>4936</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1102,8 +1189,8 @@
         <v>48</v>
       </c>
       <c r="G17" s="3">
-        <f>SUM(G2:G13)</f>
-        <v>83.064999999999998</v>
+        <f>SUM(G2:G15)</f>
+        <v>81.344999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1111,8 +1198,8 @@
         <v>49</v>
       </c>
       <c r="G18" s="3">
-        <f>SUM(G7:G13)</f>
-        <v>18.02</v>
+        <f>SUM(G7:G15)</f>
+        <v>16.299999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -1129,7 +1216,7 @@
         <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
         <v>53</v>
@@ -1148,7 +1235,7 @@
       </c>
       <c r="G21" s="3">
         <f>G18+G20</f>
-        <v>55.019999999999996</v>
+        <v>53.3</v>
       </c>
     </row>
   </sheetData>

--- a/Accelerometer Parts List.xlsx
+++ b/Accelerometer Parts List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlguy\New Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC813DD-81A4-4FDB-B984-6F36FB9C2E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8212C69C-D7C0-4A86-B9B5-962845DF0E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>Part Description</t>
   </si>
@@ -113,42 +113,15 @@
     <t>Already purchased</t>
   </si>
   <si>
-    <t>MicroSD card breakout board+</t>
-  </si>
-  <si>
-    <t>1528-1462-ND</t>
-  </si>
-  <si>
-    <t>https://www.adafruit.com/product/254?srsltid=AfmBOooT_5DZd4yh9DVa90nYezWdjtuGyl5zyrwDUgcpNdQAY1_4Q5Rc</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/254/5761230</t>
-  </si>
-  <si>
-    <t>JST-PH 2-Pin SMT Right Angle Connector:</t>
-  </si>
-  <si>
     <t>JST</t>
   </si>
   <si>
-    <t>1769 (Adafruit)</t>
-  </si>
-  <si>
     <t>https://www.adafruit.com/product/1769#technical-details</t>
   </si>
   <si>
     <t>Hard to find info on this one, might want to find another solution</t>
   </si>
   <si>
-    <t>JST PH 2-Pin Cable - Female Connector</t>
-  </si>
-  <si>
-    <t>261 (Adafruit</t>
-  </si>
-  <si>
-    <t>https://www.adafruit.com/product/261</t>
-  </si>
-  <si>
     <t>Capacitor (Bulk) MLCC 100μF 10V X5R 1206</t>
   </si>
   <si>
@@ -269,31 +242,70 @@
     <t>https://www.digikey.com/en/products/detail/walsin-technology-corporation/1206X106K500CT/17808791</t>
   </si>
   <si>
-    <t>4 pin header for OLED screen</t>
-  </si>
-  <si>
-    <t>4 pin cable for OLED screen</t>
-  </si>
-  <si>
-    <t>1528-4936-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4936/14552171?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20232005509&amp;gbraid=0AAAAADrbLljFhl6uxaG6Vfs0W7q6jx3ii&amp;gclid=CjwKCAjwtvvPBhBuEiwAPMijr5ie0JUE-YVr1s3BIn2YI-rPrlRl3aUK7X-S9cMlmjBsBVxlI5H4CBoCar0QAvD_BwE</t>
-  </si>
-  <si>
-    <t>https://www.adafruit.com/product/4936?srsltid=AfmBOoo60DuJxW7WVv9vNaFsUrHA5rsTkGxvHVOqGC14XekH9bkWL0r-</t>
-  </si>
-  <si>
-    <t>Harwin Inc.</t>
-  </si>
-  <si>
-    <t>M20-8770442</t>
-  </si>
-  <si>
-    <t>952-2353-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/harwin-inc/M20-8770442/3906342?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=17336967819&amp;gbraid=0AAAAADrbLljy55Q_fHYkiYfayGZku53Hu&amp;gclid=CjwKCAjwtvvPBhBuEiwAPMijrwmD32zTwh_m_WWuadgRad4clHmqjZAHfx3jsvLfpQkKoRUu3SWI_xoCH1IQAvD_BwE</t>
+    <t>MicroSD Card Socket</t>
+  </si>
+  <si>
+    <t>Molex</t>
+  </si>
+  <si>
+    <t>WM11190CT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/5033981892/4555393</t>
+  </si>
+  <si>
+    <t>100k Pull-Up resistor</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>RC0603JR-07100KL</t>
+  </si>
+  <si>
+    <t>311-100KGRCT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-07100KL/726698</t>
+  </si>
+  <si>
+    <t>S2B-PH-SM4-TB</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/S2B-PH-SM4-TB/926655</t>
+  </si>
+  <si>
+    <t>455-S2B-PH-SM4-TBCT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/PHR-2/608607</t>
+  </si>
+  <si>
+    <t>JST PH 2-Pin SMT Right Angle Connector</t>
+  </si>
+  <si>
+    <t>JST-PH 2-Pin male connector /female pins</t>
+  </si>
+  <si>
+    <t>455-1165-ND</t>
+  </si>
+  <si>
+    <t>PHR-2</t>
+  </si>
+  <si>
+    <t>Sullins Connector Solutions</t>
+  </si>
+  <si>
+    <t>CONN HDR 4POS 0.1 TIN SMD</t>
+  </si>
+  <si>
+    <t>NPTC041KFXC-RC</t>
+  </si>
+  <si>
+    <t>S5596-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/NPTC041KFXC-RC/776054</t>
   </si>
 </sst>
 </file>
@@ -693,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
@@ -758,7 +770,7 @@
         <v>24.95</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" ref="G2:G13" si="0">E2*F2</f>
+        <f t="shared" ref="G2:G4" si="0">E2*F2</f>
         <v>24.95</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -838,404 +850,392 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.105</v>
+      </c>
+      <c r="G5" s="3">
+        <f>E5*F5</f>
+        <v>3.105</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>254</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" ref="G6" si="1">E6*F6</f>
+        <v>0.49</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="G5" s="3">
-        <f t="shared" si="0"/>
-        <v>7.5</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="I6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>3.105</v>
-      </c>
-      <c r="G6" s="3">
-        <f>E6*F6</f>
-        <v>3.105</v>
-      </c>
-      <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="3">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>36</v>
+        <f>E7*F7</f>
+        <v>0.1</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>33</v>
+        <v>80</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="3">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="G8" s="3">
         <f>E8*F8</f>
-        <v>0.75</v>
-      </c>
-      <c r="H8" s="4" t="s">
+        <v>0.49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>0.49</v>
+        <v>0.61</v>
       </c>
       <c r="G9" s="3">
-        <f>E9*F9</f>
-        <v>0.49</v>
+        <f t="shared" ref="G9:G16" si="2">E9*F9</f>
+        <v>0.61</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" s="3">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" ref="G10:G15" si="1">E10*F10</f>
-        <v>0.61</v>
+        <f t="shared" si="2"/>
+        <v>0.19</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" t="s">
-        <v>47</v>
+      <c r="I10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11">
+      <c r="A11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="6">
+        <v>4</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="F11" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>0.19</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="F12" s="3">
+        <v>11.99</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="2"/>
+        <v>11.99</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" t="s">
         <v>12</v>
-      </c>
-      <c r="I11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="6">
-        <v>4</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" s="3">
-        <v>11.99</v>
+        <v>0.65</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="1"/>
-        <v>11.99</v>
-      </c>
-      <c r="H13" t="s">
-        <v>66</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="I13" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
+        <v>69</v>
+      </c>
+      <c r="C14">
+        <v>5033981892</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" s="3">
-        <v>0.37</v>
+        <v>2.62</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="1"/>
-        <v>0.37</v>
+        <f>E14*F14</f>
+        <v>2.62</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>4936</v>
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="H15" t="s">
-        <v>81</v>
+        <f>E15*F15</f>
+        <v>0.2</v>
       </c>
       <c r="I15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="3">
-        <f>SUM(G2:G15)</f>
-        <v>81.344999999999999</v>
+      <c r="A17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3">
-        <f>SUM(G7:G15)</f>
-        <v>16.299999999999997</v>
+        <f>SUM(G2:G15)</f>
+        <v>75.285000000000011</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="3"/>
+      <c r="F19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="3">
+        <f>SUM(G6:G15)</f>
+        <v>17.739999999999998</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="3">
+        <v>43</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="3">
         <f>5*7.4</f>
         <v>37</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="3">
-        <f>G18+G20</f>
-        <v>53.3</v>
+      <c r="H21" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="3">
+        <f>G19+G21</f>
+        <v>54.739999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -1244,16 +1244,11 @@
     <hyperlink ref="H3" r:id="rId2" xr:uid="{2784756E-0EC6-4BC1-B2C1-C7580AEF6D01}"/>
     <hyperlink ref="H4" r:id="rId3" xr:uid="{460AA21F-E8E8-41BA-9AE4-C302019B0ADD}"/>
     <hyperlink ref="I4" r:id="rId4" xr:uid="{0958AB66-BC26-43D3-B4E6-F77147ECE925}"/>
-    <hyperlink ref="H5" r:id="rId5" xr:uid="{8BB4E4AE-81D7-4BF0-82F4-7F63AA342847}"/>
-    <hyperlink ref="I5" r:id="rId6" xr:uid="{448BCD77-1BDB-4AD2-A349-F89968C0BF85}"/>
-    <hyperlink ref="H8" r:id="rId7" location="technical-details" xr:uid="{419C7ACC-0298-459D-897D-5056B5D5CED7}"/>
-    <hyperlink ref="H7" r:id="rId8" xr:uid="{6E41EBE0-4F31-43FC-B32F-414758DB6E5C}"/>
-    <hyperlink ref="I9" r:id="rId9" xr:uid="{F0494416-5BEA-4EBA-A327-5ADC3DC2DDA8}"/>
-    <hyperlink ref="I10" r:id="rId10" xr:uid="{D4B10341-E987-45F2-8B14-30FB38AA6CBF}"/>
-    <hyperlink ref="H20" r:id="rId11" xr:uid="{F00F8E76-9440-41F1-9983-F88FE3FF92F9}"/>
-    <hyperlink ref="I12" r:id="rId12" xr:uid="{0F322E2E-AA60-40C6-B37D-CE5A8F17710F}"/>
+    <hyperlink ref="H21" r:id="rId5" xr:uid="{F00F8E76-9440-41F1-9983-F88FE3FF92F9}"/>
+    <hyperlink ref="H6" r:id="rId6" location="technical-details" xr:uid="{2DF40FBC-FC77-4FBB-927F-4F592874E487}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{4611F87B-6738-49CF-BABA-7107C1E2B1D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/Accelerometer Parts List.xlsx
+++ b/Accelerometer Parts List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlguy\New Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8212C69C-D7C0-4A86-B9B5-962845DF0E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413603B5-E080-4E3A-B4B6-93CAD2686039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="100">
   <si>
     <t>Part Description</t>
   </si>
@@ -254,21 +254,9 @@
     <t>https://www.digikey.com/en/products/detail/molex/5033981892/4555393</t>
   </si>
   <si>
-    <t>100k Pull-Up resistor</t>
-  </si>
-  <si>
     <t>Yageo</t>
   </si>
   <si>
-    <t>RC0603JR-07100KL</t>
-  </si>
-  <si>
-    <t>311-100KGRCT-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-07100KL/726698</t>
-  </si>
-  <si>
     <t>S2B-PH-SM4-TB</t>
   </si>
   <si>
@@ -306,6 +294,48 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/NPTC041KFXC-RC/776054</t>
+  </si>
+  <si>
+    <t>2315-SBF32202ASTPCT-ND</t>
+  </si>
+  <si>
+    <t>Kamaya Inc.</t>
+  </si>
+  <si>
+    <t>SBF32202ASTP</t>
+  </si>
+  <si>
+    <t>FUSE CHIP 2A 63VDC 1206</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kamaya-inc/SBF32202ASTP/15181240</t>
+  </si>
+  <si>
+    <t>Tactile Switch SPST-NO Top Actuated Surface Mount</t>
+  </si>
+  <si>
+    <t>Same Sky (Formerly CUI Devices)</t>
+  </si>
+  <si>
+    <t>TS04-66-43-BK-260-SMT</t>
+  </si>
+  <si>
+    <t>2223-TS04-66-43-BK-260-SMT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/same-sky-formerly-cui-devices-/TS04-66-43-BK-260-SMT/15634271?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20243136172&amp;gbraid=0AAAAADrbLlgNZPd9mGWIN23T4v4hQaimo&amp;gclid=CjwKCAjwxITRBhBYEiwA6mZm7XXHRlZ7B4iS8uxiXAc_mfLRorsd6CdeZ8a5MGYDofd54wN73_n2DBoCCGsQAvD_BwE</t>
+  </si>
+  <si>
+    <t>RES 100K OHM 1% 1/8W 0805</t>
+  </si>
+  <si>
+    <t>RC0805FR-07100KL</t>
+  </si>
+  <si>
+    <t>311-100KCRCT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0805FR-07100KL/727544</t>
   </si>
 </sst>
 </file>
@@ -705,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
@@ -884,16 +914,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -909,7 +939,7 @@
         <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>27</v>
@@ -917,16 +947,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -939,7 +969,7 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s">
         <v>27</v>
@@ -995,7 +1025,7 @@
         <v>0.61</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" ref="G9:G16" si="2">E9*F9</f>
+        <f t="shared" ref="G9:G13" si="2">E9*F9</f>
         <v>0.61</v>
       </c>
       <c r="H9" t="s">
@@ -1100,16 +1130,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1122,7 +1152,7 @@
         <v>0.65</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -1154,16 +1184,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
         <v>72</v>
       </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1176,65 +1206,119 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G16" s="3">
+        <f>E16*F16</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="3">
+        <f>E17*F17</f>
+        <v>0.4</v>
+      </c>
+      <c r="I17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F18" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F19" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="3">
-        <f>SUM(G2:G15)</f>
-        <v>75.285000000000011</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F19" t="s">
+      <c r="G19" s="3">
+        <f>SUM(G2:G17)</f>
+        <v>75.965000000000018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F20" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G20" s="3">
         <f>SUM(G6:G15)</f>
         <v>17.739999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E20" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>41</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>42</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>62</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G22" s="3">
         <f>5*7.4</f>
         <v>37</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F22" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F23" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="3">
-        <f>G19+G21</f>
+      <c r="G23" s="3">
+        <f>G20+G22</f>
         <v>54.739999999999995</v>
       </c>
     </row>
@@ -1244,7 +1328,7 @@
     <hyperlink ref="H3" r:id="rId2" xr:uid="{2784756E-0EC6-4BC1-B2C1-C7580AEF6D01}"/>
     <hyperlink ref="H4" r:id="rId3" xr:uid="{460AA21F-E8E8-41BA-9AE4-C302019B0ADD}"/>
     <hyperlink ref="I4" r:id="rId4" xr:uid="{0958AB66-BC26-43D3-B4E6-F77147ECE925}"/>
-    <hyperlink ref="H21" r:id="rId5" xr:uid="{F00F8E76-9440-41F1-9983-F88FE3FF92F9}"/>
+    <hyperlink ref="H22" r:id="rId5" xr:uid="{F00F8E76-9440-41F1-9983-F88FE3FF92F9}"/>
     <hyperlink ref="H6" r:id="rId6" location="technical-details" xr:uid="{2DF40FBC-FC77-4FBB-927F-4F592874E487}"/>
     <hyperlink ref="H12" r:id="rId7" xr:uid="{4611F87B-6738-49CF-BABA-7107C1E2B1D5}"/>
   </hyperlinks>

--- a/Accelerometer Parts List.xlsx
+++ b/Accelerometer Parts List.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlguy\New Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413603B5-E080-4E3A-B4B6-93CAD2686039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D82D00-9963-4119-97A4-488CA5ADF99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="First Accelerometer PCB Order" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="120">
   <si>
     <t>Part Description</t>
   </si>
@@ -336,14 +337,75 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/yageo/RC0805FR-07100KL/727544</t>
+  </si>
+  <si>
+    <t>need to figure out wire gauge we are using</t>
+  </si>
+  <si>
+    <t>OshPark</t>
+  </si>
+  <si>
+    <t>OshStencil</t>
+  </si>
+  <si>
+    <t>Notes: For first order, we already have the swan, the clock, the accelerometer, the batteries, an OLED screen, and plenty of buttons</t>
+  </si>
+  <si>
+    <t>Total:</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/SPH-002T-P0-5S/26216268</t>
+  </si>
+  <si>
+    <t>455-1127-100-ND</t>
+  </si>
+  <si>
+    <t>SPH-002T-P0.5S</t>
+  </si>
+  <si>
+    <t>CONN SOCKET 24-30AWG CRIMP TIN</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/1007-24-1-2000-001-1-TS/28220524</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/1007-24-1-2000-004-1-TS/28220605</t>
+  </si>
+  <si>
+    <t>Paste Stencil</t>
+  </si>
+  <si>
+    <t>https://oshpark.com/shared_projects/LVQwHZoq</t>
+  </si>
+  <si>
+    <t>CNC Tech</t>
+  </si>
+  <si>
+    <t>1175-1007-24-1-2000-004-1-TS-ND</t>
+  </si>
+  <si>
+    <t>1007-24-1-2000-004-1-TS</t>
+  </si>
+  <si>
+    <t>WIRE 24AWG RED STRAND FEET</t>
+  </si>
+  <si>
+    <t>1175-1007-24-1-2000-001-1-TS-ND</t>
+  </si>
+  <si>
+    <t>WIRE 24AWG BLK STRAND FEET</t>
+  </si>
+  <si>
+    <t>1007-24-1-2000-001-1-TS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -411,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -420,6 +482,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -735,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
@@ -968,7 +1032,7 @@
         <f>E7*F7</f>
         <v>0.1</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="4" t="s">
         <v>76</v>
       </c>
       <c r="J7" t="s">
@@ -1320,6 +1384,11 @@
       <c r="G23" s="3">
         <f>G20+G22</f>
         <v>54.739999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1331,8 +1400,441 @@
     <hyperlink ref="H22" r:id="rId5" xr:uid="{F00F8E76-9440-41F1-9983-F88FE3FF92F9}"/>
     <hyperlink ref="H6" r:id="rId6" location="technical-details" xr:uid="{2DF40FBC-FC77-4FBB-927F-4F592874E487}"/>
     <hyperlink ref="H12" r:id="rId7" xr:uid="{4611F87B-6738-49CF-BABA-7107C1E2B1D5}"/>
+    <hyperlink ref="I7" r:id="rId8" xr:uid="{6C75CCA2-2FCB-44F0-BAA5-0079A3856A71}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE43E244-E934-476D-A364-71F29400FAE1}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="8.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" customWidth="1"/>
+    <col min="7" max="8" width="14.1796875" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0.49</v>
+      </c>
+      <c r="G2" s="3">
+        <f t="shared" ref="G2" si="0">E2*F2</f>
+        <v>1.47</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="3">
+        <f>E3*F3</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4" s="8">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" ref="G4:G10" si="1">E4*F4</f>
+        <v>4.09</v>
+      </c>
+      <c r="H4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.49</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="1"/>
+        <v>1.47</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.61</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>1.83</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="6">
+        <v>20</v>
+      </c>
+      <c r="F7" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.68</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9500000000000002</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.34</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10">
+        <v>5033981892</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="G10" s="3">
+        <f>E10*F10</f>
+        <v>7.86</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.439</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" ref="G11:G12" si="2">E11*F11</f>
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="H11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.439</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="2"/>
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="H12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>32.950000000000003</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" ref="G13:G14" si="3">E14*F14</f>
+        <v>32.950000000000003</v>
+      </c>
+      <c r="H14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="3">
+        <f>SUM(G2:G14)</f>
+        <v>61.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{C0FAAA57-36CF-4FD4-B1C5-2E553F7E135C}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{BB6A0EF0-CA79-4DA5-BC3B-A25585134DD4}"/>
+    <hyperlink ref="I2" r:id="rId3" xr:uid="{019A236E-D2DB-4CB1-90AB-7CF61FEC7D33}"/>
+    <hyperlink ref="H3" r:id="rId4" xr:uid="{CF106BCC-1B59-40D2-84C6-969F8BAEA402}"/>
+    <hyperlink ref="H7" r:id="rId5" xr:uid="{E4B1C75A-C253-4D42-AA8F-162D4E4EB9F6}"/>
+    <hyperlink ref="H5" r:id="rId6" xr:uid="{A381883F-7E88-486C-84C5-7002F7CBB814}"/>
+    <hyperlink ref="H6" r:id="rId7" xr:uid="{B38C5576-E2C0-47C0-8454-B5FAB3F28022}"/>
+    <hyperlink ref="H9" r:id="rId8" xr:uid="{E6937922-3549-4B98-A42F-FAA02C8572BF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>